--- a/main/ig/StructureDefinition-fr-medicationrequest.xlsx
+++ b/main/ig/StructureDefinition-fr-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T14:23:51+00:00</t>
+    <t>2026-08-03T12:01:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-medicationrequest.xlsx
+++ b/main/ig/StructureDefinition-fr-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T12:01:42+00:00</t>
+    <t>2026-08-03T12:24:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
